--- a/Masterdata/Materials.xlsx
+++ b/Masterdata/Materials.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F61999F-7C59-47F2-9220-F5893166C4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51965A47-3230-44B8-9055-B3DF6C7E6672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-55080" yWindow="2730" windowWidth="21600" windowHeight="12525" xr2:uid="{A8B817EE-B692-4E35-9DD7-8FB9369AB787}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{A8B817EE-B692-4E35-9DD7-8FB9369AB787}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
   <si>
     <t>Density</t>
   </si>
@@ -200,40 +200,16 @@
     <t>EN AW-6082 T6</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>https://www.theworldmaterial.com/6082-aluminum/</t>
-  </si>
-  <si>
-    <t>European structural alloy; suitable for premium machined and anodised parts.</t>
-  </si>
-  <si>
     <t>AL6061</t>
   </si>
   <si>
     <t>AA 6061-T6</t>
   </si>
   <si>
-    <t>https://www.theworldmaterial.com/al-6061-t6-aluminum-alloy/</t>
-  </si>
-  <si>
-    <t>General-purpose wrought alloy with good machinability and corrosion resistance.</t>
-  </si>
-  <si>
     <t>ADC12</t>
   </si>
   <si>
-    <t>https://www.ycumetal.com/density-of-aluminum-alloys/</t>
-  </si>
-  <si>
-    <t>High-volume die-casting alloy; verify cosmetic surface and porosity requirements.</t>
-  </si>
-  <si>
     <t>A380</t>
-  </si>
-  <si>
-    <t>Common HPDC alloy for housings and structural components.</t>
   </si>
 </sst>
 </file>
@@ -626,14 +602,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0E898A-B1E8-4C3D-BF2B-E23091F7DDB8}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="26.90625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -650,7 +625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>51</v>
       </c>
@@ -666,15 +641,13 @@
       <c r="E2" s="3">
         <v>3.5</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>1</v>
@@ -685,15 +658,13 @@
       <c r="E3" s="3">
         <v>3.4</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>1</v>
@@ -704,15 +675,13 @@
       <c r="E4" s="3">
         <v>2.8</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>1</v>
@@ -723,10 +692,8 @@
       <c r="E5" s="3">
         <v>2.9</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -743,7 +710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -760,7 +727,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
@@ -777,7 +744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -794,7 +761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
@@ -811,7 +778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -828,7 +795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -845,7 +812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -862,7 +829,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
@@ -879,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>31</v>
       </c>
@@ -896,7 +863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
@@ -913,7 +880,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
@@ -930,7 +897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
@@ -947,7 +914,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>39</v>
       </c>
@@ -964,7 +931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>40</v>
       </c>
@@ -981,7 +948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>42</v>
       </c>
@@ -998,7 +965,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>44</v>
       </c>
@@ -1015,7 +982,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>47</v>
       </c>
@@ -1032,7 +999,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>49</v>
       </c>
@@ -1049,50 +1016,10 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="K27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="K28" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="K29" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="K30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
+    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
